--- a/erp-server/erp-server-oms/src/main/resources/excel/kolB2bApplicationTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/kolB2bApplicationTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <r>
       <rPr>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>项目名称</t>
+  </si>
+  <si>
+    <t>明细备注</t>
   </si>
 </sst>
 </file>
@@ -1268,7 +1271,7 @@
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/kolB2bApplicationTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/kolB2bApplicationTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="24945" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="B2B寄样申请导入模板" sheetId="1" r:id="rId1"/>
@@ -1275,6 +1275,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1 K2 K3:K1048576">
+      <formula1>"货代地址,收货地址,公司地址"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
